--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,430 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129688237</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91603</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skålvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>537745</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6870457</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129688659</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80176</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backarvall, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>537877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6870447</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129688238</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79071</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skålvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537740</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6870450</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129688660</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80176</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Backarvall, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537855</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6870430</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79071</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129688659</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129688238</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79748230</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537746.0539431736</v>
+        <v>537746</v>
       </c>
       <c r="R2" t="n">
-        <v>6870456.794969412</v>
+        <v>6870457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2018-05-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-05-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,7 +780,7 @@
         <v>129688237</v>
       </c>
       <c r="B3" t="n">
-        <v>91644</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688659</v>
+        <v>129688238</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,14 +918,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Skålvallen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537877</v>
+        <v>537740</v>
       </c>
       <c r="R4" t="n">
-        <v>6870447</v>
+        <v>6870450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129688238</v>
+        <v>129688659</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1039,14 +1024,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skålvallen, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537740</v>
+        <v>537877</v>
       </c>
       <c r="R5" t="n">
-        <v>6870450</v>
+        <v>6870447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1113,7 +1098,7 @@
         <v>129688660</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55108-2025 artfynd.xlsx
+++ b/artfynd/A 55108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79748230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,8 +1223,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688660</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>